--- a/artfynd/A 3966-2025 artfynd.xlsx
+++ b/artfynd/A 3966-2025 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132476400</v>
+        <v>132476401</v>
       </c>
       <c r="B4" t="n">
-        <v>57945</v>
+        <v>91842</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,35 +906,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -942,13 +933,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561769</v>
+        <v>561593</v>
       </c>
       <c r="R4" t="n">
-        <v>6917327</v>
+        <v>6917323</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132476401</v>
+        <v>132476400</v>
       </c>
       <c r="B5" t="n">
-        <v>91842</v>
+        <v>57945</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,26 +1016,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561593</v>
+        <v>561769</v>
       </c>
       <c r="R5" t="n">
-        <v>6917323</v>
+        <v>6917327</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 3966-2025 artfynd.xlsx
+++ b/artfynd/A 3966-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132476402</v>
       </c>
       <c r="B2" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>132476406</v>
       </c>
       <c r="B3" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>132476401</v>
       </c>
       <c r="B4" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>132476400</v>
       </c>
       <c r="B5" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>132476416</v>
       </c>
       <c r="B6" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>132476414</v>
       </c>
       <c r="B7" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,38 +1350,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132476419</v>
+        <v>132476405</v>
       </c>
       <c r="B8" t="n">
-        <v>99098</v>
+        <v>92197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1389,13 +1388,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561766</v>
+        <v>561686</v>
       </c>
       <c r="R8" t="n">
-        <v>6917317</v>
+        <v>6917341</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,7 +1423,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,7 +1433,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,37 +1460,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132476405</v>
+        <v>132476419</v>
       </c>
       <c r="B9" t="n">
-        <v>92191</v>
+        <v>99106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561686</v>
+        <v>561766</v>
       </c>
       <c r="R9" t="n">
-        <v>6917341</v>
+        <v>6917317</v>
       </c>
       <c r="S9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,42 +1571,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132476408</v>
+        <v>132476399</v>
       </c>
       <c r="B10" t="n">
-        <v>99098</v>
+        <v>57137</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1614,13 +1618,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561641</v>
+        <v>561684</v>
       </c>
       <c r="R10" t="n">
-        <v>6917315</v>
+        <v>6917327</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1649,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,46 +1690,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132476399</v>
+        <v>132476408</v>
       </c>
       <c r="B11" t="n">
-        <v>57136</v>
+        <v>99106</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1733,13 +1733,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561684</v>
+        <v>561641</v>
       </c>
       <c r="R11" t="n">
-        <v>6917327</v>
+        <v>6917315</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,7 +1808,7 @@
         <v>132476404</v>
       </c>
       <c r="B12" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>132476418</v>
       </c>
       <c r="B13" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>132476398</v>
       </c>
       <c r="B14" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>132476409</v>
       </c>
       <c r="B15" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>132476407</v>
       </c>
       <c r="B16" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>132476410</v>
       </c>
       <c r="B17" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>132476413</v>
       </c>
       <c r="B18" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>132476417</v>
       </c>
       <c r="B19" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 3966-2025 artfynd.xlsx
+++ b/artfynd/A 3966-2025 artfynd.xlsx
@@ -1571,46 +1571,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132476399</v>
+        <v>132476408</v>
       </c>
       <c r="B10" t="n">
-        <v>57137</v>
+        <v>99106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1618,13 +1614,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561684</v>
+        <v>561641</v>
       </c>
       <c r="R10" t="n">
-        <v>6917327</v>
+        <v>6917315</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1653,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,42 +1686,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132476408</v>
+        <v>132476399</v>
       </c>
       <c r="B11" t="n">
-        <v>99106</v>
+        <v>57137</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1733,13 +1733,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561641</v>
+        <v>561684</v>
       </c>
       <c r="R11" t="n">
-        <v>6917315</v>
+        <v>6917327</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1915,52 +1915,60 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132476418</v>
+        <v>132476398</v>
       </c>
       <c r="B13" t="n">
-        <v>99106</v>
+        <v>57137</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nyängena, Nyängena, Mpd</t>
+          <t>Nyängena, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>561734</v>
+        <v>561640</v>
       </c>
       <c r="R13" t="n">
-        <v>6917342</v>
+        <v>6917273</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1989,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1999,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2026,60 +2034,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132476398</v>
+        <v>132476418</v>
       </c>
       <c r="B14" t="n">
-        <v>57137</v>
+        <v>99106</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nyängena, Mpd</t>
+          <t>Nyängena, Nyängena, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>561640</v>
+        <v>561734</v>
       </c>
       <c r="R14" t="n">
-        <v>6917273</v>
+        <v>6917342</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 3966-2025 artfynd.xlsx
+++ b/artfynd/A 3966-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132476402</v>
       </c>
       <c r="B2" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>132476406</v>
       </c>
       <c r="B3" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>132476401</v>
       </c>
       <c r="B4" t="n">
-        <v>91848</v>
+        <v>91858</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>132476400</v>
       </c>
       <c r="B5" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>132476416</v>
       </c>
       <c r="B6" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>132476414</v>
       </c>
       <c r="B7" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,37 +1350,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132476405</v>
+        <v>132476419</v>
       </c>
       <c r="B8" t="n">
-        <v>92197</v>
+        <v>99116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1388,13 +1389,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561686</v>
+        <v>561766</v>
       </c>
       <c r="R8" t="n">
-        <v>6917341</v>
+        <v>6917317</v>
       </c>
       <c r="S8" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1423,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1433,7 +1434,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,38 +1461,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132476419</v>
+        <v>132476405</v>
       </c>
       <c r="B9" t="n">
-        <v>99106</v>
+        <v>92207</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561766</v>
+        <v>561686</v>
       </c>
       <c r="R9" t="n">
-        <v>6917317</v>
+        <v>6917341</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,42 +1571,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132476408</v>
+        <v>132476399</v>
       </c>
       <c r="B10" t="n">
-        <v>99106</v>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1614,13 +1618,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561641</v>
+        <v>561684</v>
       </c>
       <c r="R10" t="n">
-        <v>6917315</v>
+        <v>6917327</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1649,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,46 +1690,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132476399</v>
+        <v>132476408</v>
       </c>
       <c r="B11" t="n">
-        <v>57137</v>
+        <v>99116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1733,13 +1733,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561684</v>
+        <v>561641</v>
       </c>
       <c r="R11" t="n">
-        <v>6917327</v>
+        <v>6917315</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,7 +1808,7 @@
         <v>132476404</v>
       </c>
       <c r="B12" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,60 +1915,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132476398</v>
+        <v>132476418</v>
       </c>
       <c r="B13" t="n">
-        <v>57137</v>
+        <v>99116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nyängena, Mpd</t>
+          <t>Nyängena, Nyängena, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>561640</v>
+        <v>561734</v>
       </c>
       <c r="R13" t="n">
-        <v>6917273</v>
+        <v>6917342</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1997,7 +1989,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +1999,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,52 +2026,60 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132476418</v>
+        <v>132476398</v>
       </c>
       <c r="B14" t="n">
-        <v>99106</v>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nyängena, Nyängena, Mpd</t>
+          <t>Nyängena, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>561734</v>
+        <v>561640</v>
       </c>
       <c r="R14" t="n">
-        <v>6917342</v>
+        <v>6917273</v>
       </c>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,7 +2148,7 @@
         <v>132476409</v>
       </c>
       <c r="B15" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>132476407</v>
       </c>
       <c r="B16" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>132476410</v>
       </c>
       <c r="B17" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>132476413</v>
       </c>
       <c r="B18" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>132476417</v>
       </c>
       <c r="B19" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 3966-2025 artfynd.xlsx
+++ b/artfynd/A 3966-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132476402</v>
       </c>
       <c r="B2" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>132476406</v>
       </c>
       <c r="B3" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>132476401</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>91859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>132476416</v>
       </c>
       <c r="B6" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>132476414</v>
       </c>
       <c r="B7" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>132476419</v>
       </c>
       <c r="B8" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>132476405</v>
       </c>
       <c r="B9" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,46 +1571,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132476399</v>
+        <v>132476408</v>
       </c>
       <c r="B10" t="n">
-        <v>57141</v>
+        <v>99117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1618,13 +1614,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561684</v>
+        <v>561641</v>
       </c>
       <c r="R10" t="n">
-        <v>6917327</v>
+        <v>6917315</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1653,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,42 +1686,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132476408</v>
+        <v>132476399</v>
       </c>
       <c r="B11" t="n">
-        <v>99116</v>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1733,13 +1733,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561641</v>
+        <v>561684</v>
       </c>
       <c r="R11" t="n">
-        <v>6917315</v>
+        <v>6917327</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,7 +1808,7 @@
         <v>132476404</v>
       </c>
       <c r="B12" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,52 +1915,60 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132476418</v>
+        <v>132476398</v>
       </c>
       <c r="B13" t="n">
-        <v>99116</v>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nyängena, Nyängena, Mpd</t>
+          <t>Nyängena, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>561734</v>
+        <v>561640</v>
       </c>
       <c r="R13" t="n">
-        <v>6917342</v>
+        <v>6917273</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1989,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1999,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2026,60 +2034,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132476398</v>
+        <v>132476418</v>
       </c>
       <c r="B14" t="n">
-        <v>57141</v>
+        <v>99117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nyängena, Mpd</t>
+          <t>Nyängena, Nyängena, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>561640</v>
+        <v>561734</v>
       </c>
       <c r="R14" t="n">
-        <v>6917273</v>
+        <v>6917342</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,7 +2148,7 @@
         <v>132476409</v>
       </c>
       <c r="B15" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>132476407</v>
       </c>
       <c r="B16" t="n">
-        <v>97981</v>
+        <v>97982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>132476410</v>
       </c>
       <c r="B17" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>132476413</v>
       </c>
       <c r="B18" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>132476417</v>
       </c>
       <c r="B19" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 3966-2025 artfynd.xlsx
+++ b/artfynd/A 3966-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132476401</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132476405</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132476406</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132476404</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132476402</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1341,6 +1371,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132476400</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1460,6 +1495,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132476398</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1579,6 +1619,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132476399</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1694,6 +1739,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132476408</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1809,6 +1859,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132476409</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1924,6 +1979,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132476410</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2044,6 +2104,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132476413</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2159,6 +2224,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132476414</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2270,6 +2340,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132476416</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2381,6 +2456,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132476417</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2492,6 +2572,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132476418</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2603,6 +2688,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132476419</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2714,8 +2804,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132476407</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>